--- a/Configs/GameConfig/Datas/SkillActionConfig.xlsx
+++ b/Configs/GameConfig/Datas/SkillActionConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra7e51f4eed6a406c"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38d205dec33a4601"/>
   </sheets>
 </workbook>
 </file>
@@ -352,6 +352,7 @@
     <col min="11" max="11" width="28" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="38" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="38.75" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1">
@@ -393,6 +394,9 @@
       </c>
       <c r="M1" s="10" t="str">
         <v>ConsumesSecondAirJump</v>
+      </c>
+      <c r="N1" s="10" t="str">
+        <v>NormalAttackBlockSeconds</v>
       </c>
     </row>
     <row r="2" ht="23" customHeight="1">
@@ -411,6 +415,7 @@
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="10" t="str">
@@ -451,6 +456,9 @@
       </c>
       <c r="M3" s="10" t="str">
         <v>bool</v>
+      </c>
+      <c r="N3" s="10" t="str">
+        <v>float</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
@@ -469,6 +477,7 @@
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="10" t="str">
@@ -509,6 +518,9 @@
       </c>
       <c r="M5" s="10" t="str">
         <v>升龙/风暴在已跳一次时占用第二次跳跃，不施加虚构跳速</v>
+      </c>
+      <c r="N5" s="10" t="str">
+        <v>施放后普攻阻止秒数；源 Role1 timers/24，火炎突击不重设</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
@@ -549,6 +561,9 @@
       <c r="M6" s="7" t="b">
         <v>1</v>
       </c>
+      <c r="N6" s="11" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="6"/>
@@ -588,6 +603,9 @@
       <c r="M7" s="7" t="b">
         <v>0</v>
       </c>
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="6"/>
@@ -627,6 +645,9 @@
       <c r="M8" s="7" t="b">
         <v>0</v>
       </c>
+      <c r="N8" s="11" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="6"/>
@@ -666,6 +687,9 @@
       <c r="M9" s="7" t="b">
         <v>1</v>
       </c>
+      <c r="N9" s="11" t="n">
+        <v>0.4166666666666667</v>
+      </c>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="6"/>
@@ -705,6 +729,9 @@
       <c r="M10" s="7" t="b">
         <v>0</v>
       </c>
+      <c r="N10" s="11" t="n">
+        <v>0.2916666666666667</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
